--- a/florist_order_forms/028_online_plant_order_form--florist_order_forms.xlsx
+++ b/florist_order_forms/028_online_plant_order_form--florist_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>shipping_info</t>
+          <t>shipping_info_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Shipping Info 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Address 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1304,12 +1304,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'paypal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'bank_transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'stripe',_'label':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'stripe', 'label': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'square',_'label':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'square', 'label': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'authorize_net',_'label':_'authorize.net'}</t>
+          <t>authorize.net</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'authorize_net', 'label': 'Authorize.net'}</t>
+          <t>Authorize.net</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'google_pay',_'label':_'google_pay'}</t>
+          <t>google_pay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'google_pay', 'label': 'Google Pay'}</t>
+          <t>Google Pay</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'apple_pay',_'label':_'apple_pay'}</t>
+          <t>apple_pay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'apple_pay', 'label': 'Apple Pay'}</t>
+          <t>Apple Pay</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'amazon_pay',_'label':_'amazon_pay'}</t>
+          <t>amazon_pay</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'amazon_pay', 'label': 'Amazon Pay'}</t>
+          <t>Amazon Pay</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'paypal_express_checkout',_'label':_'paypal_express_checkout'}</t>
+          <t>paypal_express_checkout</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'paypal_express_checkout', 'label': 'PayPal Express Checkout'}</t>
+          <t>PayPal Express Checkout</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'skrill',_'label':_'skrill'}</t>
+          <t>skrill</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'skrill', 'label': 'Skrill'}</t>
+          <t>Skrill</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'transfer_wise',_'label':_'transferwise'}</t>
+          <t>transferwise</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'transfer_wise', 'label': 'TransferWise'}</t>
+          <t>TransferWise</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'bank_transfer_euro',_'label':_'bank_transfer_euro'}</t>
+          <t>bank_transfer_euro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'bank_transfer_euro', 'label': 'Bank Transfer Euro'}</t>
+          <t>Bank Transfer Euro</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'bank_transfer_usd',_'label':_'bank_transfer_usd'}</t>
+          <t>bank_transfer_usd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'bank_transfer_usd', 'label': 'Bank Transfer USD'}</t>
+          <t>Bank Transfer USD</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'bank_transfer_jpy',_'label':_'bank_transfer_jpy'}</t>
+          <t>bank_transfer_jpy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'bank_transfer_jpy', 'label': 'Bank Transfer JPY'}</t>
+          <t>Bank Transfer JPY</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'bank_transfer_cny',_'label':_'bank_transfer_cny'}</t>
+          <t>bank_transfer_cny</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'bank_transfer_cny', 'label': 'Bank Transfer CNY'}</t>
+          <t>Bank Transfer CNY</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'bank_transfer_cad',_'label':_'bank_transfer_cad'}</t>
+          <t>bank_transfer_cad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'bank_transfer_cad', 'label': 'Bank Transfer CAD'}</t>
+          <t>Bank Transfer CAD</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'bank_transfer_aud',_'label':_'bank_transfer_aud'}</t>
+          <t>bank_transfer_aud</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'bank_transfer_aud', 'label': 'Bank Transfer AUD'}</t>
+          <t>Bank Transfer AUD</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'bank_transfer_gbp',_'label':_'bank_transfer_gbp'}</t>
+          <t>bank_transfer_gbp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'bank_transfer_gbp', 'label': 'Bank Transfer GBP'}</t>
+          <t>Bank Transfer GBP</t>
         </is>
       </c>
     </row>
@@ -1643,29 +1643,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'bank_transfer_eur',_'label':_'bank_transfer_eur'}</t>
+          <t>bank_transfer_eur</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'bank_transfer_eur', 'label': 'Bank Transfer EUR'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_25,_'name':_'bank_transfer_cny',_'label':_'bank_transfer_cny'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 25, 'name': 'bank_transfer_cny', 'label': 'Bank Transfer CNY'}</t>
+          <t>Bank Transfer EUR</t>
         </is>
       </c>
     </row>
